--- a/data/trans_orig/P42-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P42-Edad-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180505</t>
+          <t>181135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223999</t>
+          <t>222577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180505</t>
+          <t>181135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223999</t>
+          <t>222577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242634</t>
+          <t>244056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286128</t>
+          <t>285498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242634</t>
+          <t>244056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286128</t>
+          <t>285498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>531503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>564558</t>
+          <t>564499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>531503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>564558</t>
+          <t>564499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92592</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92592</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>626484</t>
+          <t>627402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>654290</t>
+          <t>654351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>626484</t>
+          <t>627402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>654290</t>
+          <t>654351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>61322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>61322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>462432</t>
+          <t>463409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>487924</t>
+          <t>488496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>462432</t>
+          <t>463409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>487924</t>
+          <t>488496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331826</t>
+          <t>332026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360614</t>
+          <t>359792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331826</t>
+          <t>332026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360614</t>
+          <t>359792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42359</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71147</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42359</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71147</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>240000</t>
+          <t>242595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>270401</t>
+          <t>270577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240000</t>
+          <t>242595</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>270401</t>
+          <t>270577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102035</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102035</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165783</t>
+          <t>167147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203981</t>
+          <t>204107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165783</t>
+          <t>167147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203981</t>
+          <t>204107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>120520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>120520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228725</t>
+          <t>230100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271079</t>
+          <t>271207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228725</t>
+          <t>230100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271079</t>
+          <t>271207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157101</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199455</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157101</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199455</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>541648</t>
+          <t>542348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>568942</t>
+          <t>569558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>541648</t>
+          <t>542348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568942</t>
+          <t>569558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>33988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>61198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>33988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>61198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>686804</t>
+          <t>686185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>702198</t>
+          <t>702119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>686804</t>
+          <t>686185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>702198</t>
+          <t>702119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>571821</t>
+          <t>571730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>593583</t>
+          <t>593109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>571821</t>
+          <t>571730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>593583</t>
+          <t>593109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>409412</t>
+          <t>408845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429971</t>
+          <t>428835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>409412</t>
+          <t>408845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>429971</t>
+          <t>428835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281575</t>
+          <t>281502</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>308136</t>
+          <t>309122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>281575</t>
+          <t>281502</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>308136</t>
+          <t>309122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>261212</t>
+          <t>260212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296478</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261212</t>
+          <t>260212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>296478</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89271</t>
+          <t>89050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124537</t>
+          <t>125537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89271</t>
+          <t>89050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124537</t>
+          <t>125537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215274</t>
+          <t>214898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>251868</t>
+          <t>251980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215274</t>
+          <t>214898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251868</t>
+          <t>251980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138556</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>175526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138556</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>175526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>485136</t>
+          <t>482876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>512310</t>
+          <t>511536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>485136</t>
+          <t>482876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>512310</t>
+          <t>511536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>77148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>77148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>609170</t>
+          <t>609387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>631457</t>
+          <t>632555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>609170</t>
+          <t>609387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>631457</t>
+          <t>632555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>599893</t>
+          <t>601353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>622726</t>
+          <t>623588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>599893</t>
+          <t>601353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>622726</t>
+          <t>623588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43987</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43987</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>448286</t>
+          <t>448586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>471441</t>
+          <t>471776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>448286</t>
+          <t>448586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>471441</t>
+          <t>471776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>44971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>44971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>313609</t>
+          <t>313926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>339545</t>
+          <t>340254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>313609</t>
+          <t>313926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339545</t>
+          <t>340254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61964</t>
+          <t>61647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61964</t>
+          <t>61647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>286884</t>
+          <t>285462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323804</t>
+          <t>325275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286884</t>
+          <t>285462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323804</t>
+          <t>325275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -6335,12 +6335,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>71329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>71329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6902,32 +6902,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>115572</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77020</t>
+          <t>93537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119649</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6937,32 +6937,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>115572</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77020</t>
+          <t>93537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119649</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -6980,32 +6980,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160770</t>
+          <t>182960</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140664</t>
+          <t>160258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183293</t>
+          <t>204995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7015,32 +7015,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>160770</t>
+          <t>182960</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140664</t>
+          <t>160258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183293</t>
+          <t>204995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>324080</t>
+          <t>287860</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300832</t>
+          <t>269086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355087</t>
+          <t>302365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>324080</t>
+          <t>287860</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>300832</t>
+          <t>269086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355087</t>
+          <t>302365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69356</t>
+          <t>79481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>64976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92604</t>
+          <t>98255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>69356</t>
+          <t>79481</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>64976</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92604</t>
+          <t>98255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>393436</t>
+          <t>367341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7378,32 +7378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>335665</t>
+          <t>382537</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>370458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344260</t>
+          <t>392517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>335665</t>
+          <t>382537</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>370458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>344260</t>
+          <t>392517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -7456,32 +7456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>54530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7491,32 +7491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>54530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -7534,17 +7534,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>424988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7616,32 +7616,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>483122</t>
+          <t>486462</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>474651</t>
+          <t>477705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490526</t>
+          <t>493850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>483122</t>
+          <t>486462</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>474651</t>
+          <t>477705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>490526</t>
+          <t>493850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30818</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7729,32 +7729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30818</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>505469</t>
+          <t>512440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>375423</t>
+          <t>416517</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>367806</t>
+          <t>407897</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382039</t>
+          <t>423951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7889,32 +7889,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>375423</t>
+          <t>416517</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367806</t>
+          <t>407897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>382039</t>
+          <t>423951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7932,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7967,32 +7967,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>401780</t>
+          <t>447425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>298114</t>
+          <t>323253</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111926</t>
+          <t>315830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>490763</t>
+          <t>329557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>298114</t>
+          <t>323253</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111926</t>
+          <t>315830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>490763</t>
+          <t>329557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229115</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>415303</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>229115</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>415303</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>527229</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8330,32 +8330,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>331574</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293554</t>
+          <t>318830</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>313920</t>
+          <t>341766</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8365,32 +8365,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>331574</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>293554</t>
+          <t>318830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313920</t>
+          <t>341766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -8408,32 +8408,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53248</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8443,32 +8443,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53248</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -8486,17 +8486,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8521,17 +8521,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>399428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8603,32 +8603,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8681,32 +8681,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
